--- a/agentic-qe-mvp/demo-artifacts/flow-1-baseline-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-baseline-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
@@ -744,7 +744,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T03:54:20.900Z</t>
+    <t>2026-10-02T04:13:59.689Z</t>
   </si>
   <si>
     <t>Column order</t>
